--- a/templates/excel/種類別/02_指名区分.xlsx
+++ b/templates/excel/種類別/02_指名区分.xlsx
@@ -466,7 +466,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>課金単位</t>
+          <t>課金単位(何分ごと)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -543,10 +543,8 @@
       <c r="B8" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>1接客ごと</t>
-        </is>
+      <c r="C8" s="6" t="n">
+        <v>60</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
@@ -566,10 +564,8 @@
       <c r="B9" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>1接客ごと</t>
-        </is>
+      <c r="C9" s="6" t="n">
+        <v>60</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
@@ -589,10 +585,8 @@
       <c r="B10" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>1接客ごと</t>
-        </is>
+      <c r="C10" s="6" t="n">
+        <v>60</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -612,11 +606,7 @@
       <c r="B11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>1接客ごと</t>
-        </is>
-      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
           <t>なし</t>
@@ -839,8 +829,8 @@
     <dataValidation sqref="B12:B41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="数字のみで入力してください(カンマ不要)" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="C12:C41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
-      <formula1>"1接客ごと,1時間ごと"</formula1>
+    <dataValidation sqref="C12:C41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="数字のみで入力してください(カンマ不要)" type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="D12:D41" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
       <formula1>"円,%,なし"</formula1>
